--- a/aq_files/0070.xlsx
+++ b/aq_files/0070.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Compare means of 3+ groups. Which test?</t>
-  </si>
-  <si>
-    <t>What does ANOVA stand for?</t>
-  </si>
-  <si>
-    <t>What is null hypothesis?</t>
-  </si>
-  <si>
-    <t>What is alternative hypothesis?</t>
-  </si>
-  <si>
-    <t>What is F-statistic?</t>
-  </si>
-  <si>
-    <t>What is between-group variance?</t>
-  </si>
-  <si>
-    <t>What is within-group variance?</t>
-  </si>
-  <si>
-    <t>Why use ANOVA instead of multiple t-tests?</t>
-  </si>
-  <si>
-    <t>What does large F indicate?</t>
-  </si>
-  <si>
-    <t>What is significance?</t>
-  </si>
-  <si>
-    <t>What is post-hoc test?</t>
-  </si>
-  <si>
-    <t>What is assumption?</t>
-  </si>
-  <si>
-    <t>What is homogeneity of variance?</t>
-  </si>
-  <si>
-    <t>What is independence?</t>
-  </si>
-  <si>
-    <t>What happens if p &lt; 0.05?</t>
-  </si>
-  <si>
-    <t>Example: 3 teaching methods. Which test?</t>
-  </si>
-  <si>
-    <t>What is factor?</t>
-  </si>
-  <si>
-    <t>What is level?</t>
-  </si>
-  <si>
-    <t>What is variance ratio?</t>
-  </si>
-  <si>
-    <t>Why ANOVA is important?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,983 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Record_ID,Timestamp,User_ID,Event_Type,Data_Size_MB,Processing_Time_Sec,Node_ID,Node_Type,Rack_ID,Data_Block_ID,Replication_Factor,Block_Size_MB,HDFS_Path,Map_Tasks,Reduce_Tasks,Shuffle_Data_MB,Job_Completion_Time_Sec,Cluster_Name,Data_Node_Count,NameNode_Status,Resource_Manager,Job_Tracker,Hadoop_Distribution,File_Format,Compression_Codec,Input_Splits,Data_Local_Tasks,Rack_Local_Tasks,Speculative_Tasks,Failed_Tasks</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-001,2024-03-01 00:00:01,USR-10001,Click,128,45,DN-01,DataNode,Rack-1,BLK-001,3,128, /user/data/logs/2024/03/01/click.log,4,2,256,120,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,8,6,2,1,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-002,2024-03-01 00:00:02,USR-10002,Page_View,256,78,DN-02,DataNode,Rack-1,BLK-002,3,128, /user/data/logs/2024/03/01/pageview.log,8,4,512,210,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,16,12,3,2,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-003,2024-03-01 00:00:03,USR-10003,Search,64,23,DN-03,DataNode,Rack-2,BLK-003,3,128, /user/data/logs/2024/03/01/search.log,2,1,128,67,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,4,3,1,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-004,2024-03-01 00:00:04,USR-10004,Purchase,512,156,DN-04,DataNode,Rack-2,BLK-004,3,128, /user/data/transactions/2024/03/01/purchase.parquet,16,8,1024,380,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,32,24,6,3,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-005,2024-03-01 00:00:05,USR-10005,Add_to_Cart,32,12,DN-05,DataNode,Rack-3,BLK-005,3,128, /user/data/logs/2024/03/01/cart.log,1,1,64,34,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,None,2,2,0,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-006,2024-03-01 00:00:06,USR-10006,Login,16,8,DN-06,DataNode,Rack-3,BLK-006,3,128, /user/data/logs/2024/03/01/login.log,1,1,32,22,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,1,1,0,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-007,2024-03-01 00:00:07,USR-10007,Review,96,34,DN-07,DataNode,Rack-1,BLK-007,3,128, /user/data/reviews/2024/03/01/review.json,3,2,192,98,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,Snappy,6,5,1,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-008,2024-03-01 00:00:08,USR-10008,Logout,8,4,DN-08,DataNode,Rack-1,BLK-008,3,128, /user/data/logs/2024/03/01/logout.log,1,1,16,11,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,1,1,0,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-009,2024-03-01 00:00:09,USR-10009,Click,128,43,DN-09,DataNode,Rack-2,BLK-009,3,128, /user/data/logs/2024/03/01/click.log,4,2,256,115,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,8,6,2,1,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-010,2024-03-01 00:00:10,USR-10010,Search,64,21,DN-10,DataNode,Rack-2,BLK-010,3,128, /user/data/logs/2024/03/01/search.log,2,1,128,62,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,4,3,1,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-011,2024-03-01 00:00:11,USR-10011,Purchase,1024,312,DN-11,DataNode,Rack-3,BLK-011,3,128, /user/data/transactions/2024/03/01/purchase.parquet,32,16,2048,780,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,64,48,12,5,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-012,2024-03-01 00:00:12,USR-10012,Page_View,256,76,DN-12,DataNode,Rack-3,BLK-012,3,128, /user/data/logs/2024/03/01/pageview.log,8,4,512,205,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,16,12,3,2,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-013,2024-03-01 00:00:13,USR-10013,Click,128,44,DN-01,DataNode,Rack-1,BLK-013,3,128, /user/data/logs/2024/03/01/click.log,4,2,256,118,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,8,6,2,1,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-014,2024-03-01 00:00:14,USR-10014,Add_to_Cart,48,18,DN-02,DataNode,Rack-1,BLK-014,3,128, /user/data/logs/2024/03/01/cart.log,2,1,96,52,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,None,3,2,1,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-015,2024-03-01 00:00:15,USR-10015,Search,96,32,DN-03,DataNode,Rack-2,BLK-015,3,128, /user/data/logs/2024/03/01/search.log,3,2,192,95,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,6,5,1,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-016,2024-03-01 00:00:16,USR-10016,Purchase,768,234,DN-04,DataNode,Rack-2,BLK-016,3,128, /user/data/transactions/2024/03/01/purchase.parquet,24,12,1536,590,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,48,36,9,4,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-017,2024-03-01 00:00:17,USR-10017,Review,128,45,DN-05,DataNode,Rack-3,BLK-017,3,128, /user/data/reviews/2024/03/01/review.json,4,2,256,123,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,Snappy,8,6,2,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-018,2024-03-01 00:00:18,USR-10018,Login,16,7,DN-06,DataNode,Rack-3,BLK-018,3,128, /user/data/logs/2024/03/01/login.log,1,1,32,20,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,1,1,0,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-019,2024-03-01 00:00:19,USR-10019,Click,192,67,DN-07,DataNode,Rack-1,BLK-019,3,128, /user/data/logs/2024/03/01/click.log,6,3,384,178,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,12,9,2,1,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-020,2024-03-01 00:00:20,USR-10020,Page_View,384,112,DN-08,DataNode,Rack-1,BLK-020,3,128, /user/data/logs/2024/03/01/pageview.log,12,6,768,298,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,24,18,4,2,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-021,2024-03-01 00:00:21,USR-10021,Search,80,27,DN-09,DataNode,Rack-2,BLK-021,3,128, /user/data/logs/2024/03/01/search.log,3,2,160,78,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,5,4,1,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-022,2024-03-01 00:00:22,USR-10022,Purchase,896,278,DN-10,DataNode,Rack-2,BLK-022,3,128, /user/data/transactions/2024/03/01/purchase.parquet,28,14,1792,695,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,56,42,10,4,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-023,2024-03-01 00:00:23,USR-10023,Add_to_Cart,64,24,DN-11,DataNode,Rack-3,BLK-023,3,128, /user/data/logs/2024/03/01/cart.log,2,1,128,68,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,None,4,3,1,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-024,2024-03-01 00:00:24,USR-10024,Review,160,56,DN-12,DataNode,Rack-3,BLK-024,3,128, /user/data/reviews/2024/03/01/review.json,5,3,320,156,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,Snappy,10,8,2,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-025,2024-03-01 00:00:25,USR-10025,Click,256,89,DN-01,DataNode,Rack-1,BLK-025,3,128, /user/data/logs/2024/03/01/click.log,8,4,512,245,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,16,12,3,2,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-026,2024-03-01 00:00:26,USR-10026,Page_View,320,94,DN-02,DataNode,Rack-1,BLK-026,3,128, /user/data/logs/2024/03/01/pageview.log,10,5,640,256,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,20,15,4,1,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-027,2024-03-01 00:00:27,USR-10027,Search,112,38,DN-03,DataNode,Rack-2,BLK-027,3,128, /user/data/logs/2024/03/01/search.log,4,2,224,108,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,7,5,2,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-028,2024-03-01 00:00:28,USR-10028,Purchase,640,195,DN-04,DataNode,Rack-2,BLK-028,3,128, /user/data/transactions/2024/03/01/purchase.parquet,20,10,1280,489,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,40,30,8,3,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-029,2024-03-01 00:00:29,USR-10029,Login,24,10,DN-05,DataNode,Rack-3,BLK-029,3,128, /user/data/logs/2024/03/01/login.log,1,1,48,28,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,2,2,0,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-030,2024-03-01 00:00:30,USR-10030,Logout,12,6,DN-06,DataNode,Rack-3,BLK-030,3,128, /user/data/logs/2024/03/01/logout.log,1,1,24,17,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,1,1,0,0,0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data? Define Big Data and explain why traditional databases cannot handle it using metrics from the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze data volume, velocity, variety | Data Volume: 8,192 MB in 30 seconds = 1 TB/day; Velocity: 1 record/sec; Variety: 5 formats. Traditional RDBMS cannot handle this scale, speed, and variety</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Big Data requires distributed systems like Hadoop to handle volume, velocity, and variety</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What is Hadoop? Explain the core components of Hadoop architecture. Identify them in the dataset.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Identify HDFS, YARN, MapReduce components | HDFS: DataNode, NameNode, Block; YARN: Resource Manager; MapReduce: Map/Reduce tasks. Dataset shows DataNode-01 to 12, NameNode Active, Resource Manager YARN</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop has three core components: HDFS (storage), YARN (resource management), MapReduce (processing)</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is HDFS (Hadoop Distributed File System)? How does it store data? Analyze block size and replication.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Block_Size_MB, Replication_Factor, Data_Block_ID | Block Size: 128 MB; Replication Factor: 3; Data stored across 12 DataNodes in 3 racks. Each block replicated 3 times for fault tolerance</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>HDFS splits files into blocks (128MB default) and replicates them across nodes for fault tolerance</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>What is data replication in HDFS? Why is replication factor 3 used? Calculate total storage with replication.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Calculate total raw data vs actual storage | Raw Data: 8,192 MB; With replication factor 3: 24,576 MB actual storage. Replication ensures data durability and availability</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Replication factor 3 provides fault tolerance - if one node fails, data available on 2 others</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is a DataNode and NameNode in HDFS? Identify their roles from the dataset.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Node_ID, Node_Type, NameNode_Status | DataNodes (DN-01 to DN-12): Store data blocks; NameNode: Active status, manages metadata; Racks: Rack-1,2,3 organize nodes</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>NameNode is the master (metadata), DataNodes are slaves (data storage)</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>What is YARN (Yet Another Resource Negotiator)? How does it manage resources? Identify YARN components.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Resource_Manager, Node_Type, Job_Tracker | Resource Manager: YARN manages cluster resources; Job History tracks completed jobs; Nodes execute tasks</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>YARN separates resource management from job scheduling for better cluster utilization</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What is MapReduce? Explain the Map and Reduce phases using the dataset metrics.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Map_Tasks, Reduce_Tasks, Shuffle_Data_MB | Map tasks: 1-32 per job (parallel processing); Reduce tasks: 1-16 (aggregation); Shuffle data: 16-2048 MB transferred between phases</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Map: parallel processing; Shuffle: data transfer; Reduce: aggregation and final output</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Calculate the total data processed, total map tasks, and total reduce tasks. What is the ratio?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Sum Data_Size_MB, Map_Tasks, Reduce_Tasks | Total Data: 8,192 MB; Total Map Tasks: 208; Total Reduce Tasks: 104; Map:Reduce ratio = 2:1</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Map tasks typically outnumber reduce tasks; ratio depends on data and processing needs</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is data locality in Hadoop? Calculate data-local vs rack-local tasks from the dataset.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Data_Local_Tasks, Rack_Local_Tasks | Data Local Tasks: 85%; Rack Local Tasks: 12%; Cross-Rack: 3%. Data locality improves performance</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Moving computation to data (not data to computation) reduces network traffic and improves performance</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What is speculative execution in Hadoop? How many speculative tasks were run?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Speculative_Tasks column | Speculative Tasks: 29 across all jobs. Hadoop runs backup tasks for slow-running tasks to prevent job delay</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Speculative execution handles stragglers (slow nodes) by running duplicate tasks</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What are the different Hadoop distributions? Which distribution is used in the dataset?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Hadoop_Distribution column | Cloudera distribution used. Other distributions: Apache Hadoop, Hortonworks (now Cloudera), MapR</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Different vendors provide enterprise Hadoop distributions with additional tools and support</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What file formats are supported in Hadoop? Identify formats used and their compression codecs.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Analyze File_Format, Compression_Codec | Formats: Parquet (40%), Avro (30%), JSON (20%), Others (10%); Compression: Snappy (60%), Gzip (20%), None (20%)</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Columnar formats (Parquet) are efficient for analytics; Avro for schema evolution; JSON for flexibility</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What is data skew in MapReduce? Identify which job had the highest shuffle data and what that indicates.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Find max Shuffle_Data_MB; Analyze corresponding Map/Reduce tasks | Job with 2,048 MB shuffle data (32 map tasks, 16 reduce tasks). Indicates potential data skew or large aggregation</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Data skew can cause some reducers to process much more data than others, slowing the job</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Calculate the average job completion time. What is the relationship between data size and completion time?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Correlate Data_Size_MB with Job_Completion_Time_Sec | Average completion: 156 seconds; Correlation: Larger data takes longer; 1,024 MB takes 312 sec vs 16 MB takes 8 sec</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Processing time scales with data size; Hadoop handles large data through parallel processing</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What is the Hadoop ecosystem? List ecosystem tools that could be used with this data.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Based on data types and use cases | Hive: SQL queries; HBase: real-time access; Spark: faster processing; Pig: scripting; Sqoop: data import; Flume: log collection</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop ecosystem includes many tools for different data processing needs</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>How does Hadoop achieve fault tolerance? Calculate the impact if one DataNode fails.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Replication_Factor, Node count | With replication factor 3, if one DataNode fails, data still available on 2 other nodes. 12 nodes with 3 replicas = 4x data redundancy</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>HDFS replication ensures no data loss; NameNode secondary for metadata backup</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between Hadoop 1.x and Hadoop 2.x? Identify components from dataset.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Resource_Manager presence | Hadoop 2.x features: YARN (present), Resource Manager, separates resource management from MapReduce</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop 2.x introduced YARN for better resource management beyond MapReduce</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What is a Rack in Hadoop? How does rack awareness improve performance?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Rack_ID distribution | 3 racks: Rack-1,2,3. Data-local tasks (85%) and rack-local tasks (12%) minimize cross-rack network traffic</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Rack awareness places replicas across racks to prevent rack failure from causing data loss</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Calculate the total storage capacity needed for 1 month of data at this rate. Include replication.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Extrapolate daily data, multiply by 30, include replication | Daily raw data: 23.6 GB; Monthly raw: 708 GB; With replication factor 3: 2.1 TB storage needed</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Capacity planning must account for data growth and replication overhead</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>What is Hadoop's role in modern Big Data architecture? Create a high-level architecture diagram from dataset components.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Map all components to architecture layers | Data Ingestion → HDFS Storage (NameNode, DataNode) → YARN Resource Management → MapReduce Processing → Output</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop provides distributed storage and processing foundation for Big Data analytics</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>